--- a/artfynd/A 49109-2021 artfynd.xlsx
+++ b/artfynd/A 49109-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49109-2021 artfynd.xlsx
+++ b/artfynd/A 49109-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88227520</v>
+        <v>88331773</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mosshöjden, Torsby, Vrm</t>
+          <t>Mosshöjden i N, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380034.8331034193</v>
+        <v>379993</v>
       </c>
       <c r="R2" t="n">
-        <v>6699767.37448251</v>
+        <v>6699591</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,39 +754,45 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrnaturskog dominerad av gran.</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Grov granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Tidemalm</t>
+          <t>Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Tidemalm, Rolf Tidemalm</t>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -791,12 +802,7 @@
         <v>88240612</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379979.3696075839</v>
+        <v>379979</v>
       </c>
       <c r="R3" t="n">
-        <v>6699677.269440794</v>
+        <v>6699677</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,19 +878,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,61 +913,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88240598</v>
+        <v>88227520</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mosshöjden i N, Vrm</t>
+          <t>Mosshöjden, Torsby, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379979.3696075839</v>
+        <v>380035</v>
       </c>
       <c r="R4" t="n">
-        <v>6699677.269440794</v>
+        <v>6699767</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,86 +982,73 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På död stam av lövträd, troligen rönn. Mycket hänglav i den östvända sluttningen. Bland annat garnlav. Stora myrstackar på höjden. 200-åriga granar i sluttningen och i den orörda sumpskogen nedanför. Även en del gamla tallar i området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm</t>
+          <t>Lars Tidemalm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Tidemalm, Lars Tidemalm</t>
+          <t>Lars Tidemalm, Rolf Tidemalm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88271126</v>
+        <v>88240598</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1089,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379979.3696075839</v>
+        <v>379979</v>
       </c>
       <c r="R5" t="n">
-        <v>6699677.269440794</v>
+        <v>6699677</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,24 +1090,14 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På smärre död stam av lövträd (rönn?). Tillsammans med bland annat lunglav och skrovellav.</t>
+          <t>På död stam av lövträd, troligen rönn. Mycket hänglav i den östvända sluttningen. Bland annat garnlav. Stora myrstackar på höjden. 200-åriga granar i sluttningen och i den orörda sumpskogen nedanför. Även en del gamla tallar i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,49 +1125,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88331773</v>
+        <v>88271126</v>
       </c>
       <c r="B6" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1106</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1218,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>379992.8476973267</v>
+        <v>379979</v>
       </c>
       <c r="R6" t="n">
-        <v>6699590.81270823</v>
+        <v>6699677</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,46 +1196,26 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På smärre död stam av lövträd (rönn?). Tillsammans med bland annat lunglav och skrovellav.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrnaturskog dominerad av gran.</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Grov granlåga</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1303,6 +1228,118 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88226023</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mustagangas,Torsby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>380158</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6699047</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vitsand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Tidemalm, Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49109-2021 artfynd.xlsx
+++ b/artfynd/A 49109-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88331773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88240612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88227520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88240598</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88271126</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,8 +1370,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88226023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>